--- a/GridSearch workflow.xlsx
+++ b/GridSearch workflow.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HOPE-AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8477F21-7DAF-413B-8AC1-65C59475A9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E53CC1F-21D0-4651-A41C-D3C13900BD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14190" yWindow="1035" windowWidth="31755" windowHeight="20685" xr2:uid="{40D48D87-E159-4681-9DE8-47022677973A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{40D48D87-E159-4681-9DE8-47022677973A}"/>
   </bookViews>
   <sheets>
-    <sheet name="05_Mc Learnin-3" sheetId="1" r:id="rId1"/>
+    <sheet name="GridSearch" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>Assign Input Variable</t>
-  </si>
-  <si>
-    <t>independent=dataset[['age', 'bmi', 'children', 'charges', 'sex_male', 'smoker_yes']]</t>
   </si>
   <si>
     <t>Assign Output Variable</t>
@@ -246,18 +243,20 @@
     <t>Assign Future Data</t>
   </si>
   <si>
+    <t>Print Future Prediction</t>
+  </si>
+  <si>
+    <t>independent=dataset[['age', 'bmi', 'children', 'sex_male', 'smoker_yes']]</t>
+  </si>
+  <si>
     <t xml:space="preserve">age_input=float(input("Age:"))
 bmi_input=float(input("BMI:"))
 children_input=float(input("Children:"))
 sex_male_input=int(input("Sex Male &lt;0 or 1&gt;:"))
-sex_female_input=int(input("Sex Female &lt;0 or 1&gt;:"))
 smoker_yes_input=int(input("Smoker Yes &lt;0 or 1&gt;:")) </t>
   </si>
   <si>
-    <t>Print Future Prediction</t>
-  </si>
-  <si>
-    <t>Future_Prediction = grid.predict([[age_input, bmi_input, children_input, sex_male_input, smoker_yes_input, sex_female_input]])
+    <t>Future_Prediction = grid.predict([[age_input, bmi_input, children_input, sex_male_input, smoker_yes_input ]])
 print("Future_Prediction={}".format(Future_Prediction))
 print("Best Parameters:", grid.best_params_)
 print("Best Score:", grid.best_score_)</t>
@@ -463,6 +462,24 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -472,27 +489,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -501,9 +503,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -529,363 +528,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>836948</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>18261</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E3693BF-A528-4F0E-A244-676BBD5E974A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="152400" y="76457175"/>
-          <a:ext cx="10019048" cy="6314286"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>504259</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123273</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BC6845D-E917-4982-B744-202793D32E5A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="266700" y="71789925"/>
-          <a:ext cx="4523809" cy="4419048"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1091181</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97997A5A-D130-4AE2-BD42-AA1865FB6F33}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="304800" y="82867500"/>
-          <a:ext cx="10120881" cy="5381625"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>989339</xdr:colOff>
-      <xdr:row>140</xdr:row>
-      <xdr:rowOff>170690</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92699471-2271-4F33-8318-A0A975BFEFCE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="238125" y="88468200"/>
-          <a:ext cx="10085714" cy="6076190"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>228599</xdr:colOff>
-      <xdr:row>142</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>866774</xdr:colOff>
-      <xdr:row>175</xdr:row>
-      <xdr:rowOff>148068</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{149304A5-9E90-4F33-8C4C-FF3BA0C3088B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="228599" y="94811850"/>
-          <a:ext cx="9972675" cy="6377418"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>176</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>838200</xdr:colOff>
-      <xdr:row>208</xdr:row>
-      <xdr:rowOff>134317</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09806294-2A3E-4F0A-B2ED-ADA07CC4B734}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="238125" y="101231700"/>
-          <a:ext cx="9934575" cy="6230317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>209</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>242</xdr:row>
-      <xdr:rowOff>89893</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Picture 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81361F12-B04F-4A84-9DA9-4ABE9F42F74D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="238125" y="107518200"/>
-          <a:ext cx="9953625" cy="6376393"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>243</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>903625</xdr:colOff>
-      <xdr:row>277</xdr:row>
-      <xdr:rowOff>56333</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5193244-D0FB-4A59-AFE7-37ECC4135A2C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="238125" y="113995200"/>
-          <a:ext cx="10000000" cy="6533333"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1203,421 +845,421 @@
   <sheetData>
     <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="21" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="3"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="9"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="6"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="7">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="10"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="7">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="10"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="6"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="7">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="11"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="12"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="7">
+      <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="11"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="12"/>
     </row>
     <row r="9" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="7">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="12" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="14"/>
+    </row>
+    <row r="10" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="13"/>
-    </row>
-    <row r="10" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7">
-        <v>6</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="14"/>
+    </row>
+    <row r="11" spans="2:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="13"/>
-    </row>
-    <row r="11" spans="2:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="14"/>
+    </row>
+    <row r="12" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="13"/>
-    </row>
-    <row r="12" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="12" t="s">
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="14"/>
+    </row>
+    <row r="13" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="13"/>
-    </row>
-    <row r="13" spans="2:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="12" t="s">
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="14"/>
+    </row>
+    <row r="14" spans="2:16" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="13"/>
-    </row>
-    <row r="14" spans="2:16" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12" t="s">
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="14"/>
+    </row>
+    <row r="15" spans="2:16" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="13"/>
-    </row>
-    <row r="15" spans="2:16" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="2:16" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="13"/>
-    </row>
-    <row r="16" spans="2:16" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="14"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="2">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="13"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="7">
-        <v>9</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="12" t="s">
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="14"/>
+    </row>
+    <row r="18" spans="2:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="13"/>
-    </row>
-    <row r="18" spans="2:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7">
-        <v>10</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="12" t="s">
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="14"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="2">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="13"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="7">
-        <v>11</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="12" t="s">
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="14"/>
+    </row>
+    <row r="20" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>12</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="13"/>
-    </row>
-    <row r="20" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7">
-        <v>12</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="14"/>
+    </row>
+    <row r="21" spans="2:16" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="3">
+        <v>13</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>40</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="13"/>
-    </row>
-    <row r="21" spans="2:16" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="14">
-        <v>13</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
@@ -1667,16 +1309,15 @@
     <mergeCell ref="I8:P8"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="I9:P9"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="I6:P6"/>
     <mergeCell ref="B3:P3"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="I4:P4"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="I5:P5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="I6:P6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>